--- a/diseases/d106/2005-2009.xlsx
+++ b/diseases/d106/2005-2009.xlsx
@@ -1970,7 +1970,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -14775,7 +14775,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -16683,7 +16683,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17637,7 +17637,7 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN90" t="b">
@@ -18591,7 +18591,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19545,7 +19545,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -22407,7 +22407,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23361,7 +23361,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -24315,7 +24315,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25672,7 +25672,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -26626,7 +26626,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27580,7 +27580,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -28534,7 +28534,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29488,7 +29488,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -30442,7 +30442,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -31396,7 +31396,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -32350,7 +32350,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -33452,7 +33452,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -34406,7 +34406,7 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN178" t="b">
@@ -35508,7 +35508,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN184" t="b">
@@ -36610,7 +36610,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -38115,7 +38115,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -39217,7 +39217,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -40319,7 +40319,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -41421,7 +41421,7 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN216" t="b">
@@ -42523,7 +42523,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -43625,7 +43625,7 @@
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN228" t="b">
@@ -44727,7 +44727,7 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN234" t="b">
@@ -45829,7 +45829,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -46931,7 +46931,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -49135,7 +49135,7 @@
       </c>
       <c r="AM258" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN258" t="b">
@@ -50237,7 +50237,7 @@
       </c>
       <c r="AM264" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN264" t="b">
@@ -52220,7 +52220,7 @@
       </c>
       <c r="AM274" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN274" t="b">
@@ -53561,7 +53561,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -54902,7 +54902,7 @@
       </c>
       <c r="AM288" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN288" t="b">
@@ -56243,7 +56243,7 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -57584,7 +57584,7 @@
       </c>
       <c r="AM302" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN302" t="b">
@@ -58925,7 +58925,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -60266,7 +60266,7 @@
       </c>
       <c r="AM316" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN316" t="b">
@@ -61607,7 +61607,7 @@
       </c>
       <c r="AM323" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN323" t="b">
@@ -62948,7 +62948,7 @@
       </c>
       <c r="AM330" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN330" t="b">
@@ -64289,7 +64289,7 @@
       </c>
       <c r="AM337" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN337" t="b">
@@ -65630,7 +65630,7 @@
       </c>
       <c r="AM344" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN344" t="b">
@@ -66971,7 +66971,7 @@
       </c>
       <c r="AM351" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN351" t="b">
